--- a/data/german_works_EdB.xlsx
+++ b/data/german_works_EdB.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>matiere</t>
+          <t>matiere_auto</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -471,7 +471,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D2" t="b">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D57" t="b">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D71" t="b">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D100" t="b">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D107" t="b">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D111" t="b">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D117" t="b">

--- a/data/german_works_EdB.xlsx
+++ b/data/german_works_EdB.xlsx
@@ -429,13 +429,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D144"/>
+  <dimension ref="A1:E144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -456,6 +457,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>is_heldenepik</t>
         </is>
       </c>
@@ -474,7 +480,12 @@
           <t>England</t>
         </is>
       </c>
-      <c r="D2" t="b">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -492,7 +503,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D3" t="b">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -510,7 +522,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D4" t="b">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -528,7 +541,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D5" t="b">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -546,7 +560,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D6" t="b">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -564,7 +579,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D7" t="b">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -582,7 +598,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D8" t="b">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -600,7 +617,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D9" t="b">
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -618,7 +636,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D10" t="b">
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -636,7 +655,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D11" t="b">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -654,7 +674,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D12" t="b">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -672,7 +693,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D13" t="b">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -690,7 +712,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D14" t="b">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="b">
         <v>1</v>
       </c>
     </row>
@@ -708,7 +731,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D15" t="b">
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -726,7 +750,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D16" t="b">
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -744,7 +769,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D17" t="b">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -762,7 +788,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D18" t="b">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -780,7 +807,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D19" t="b">
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="b">
         <v>0</v>
       </c>
     </row>
@@ -798,7 +826,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D20" t="b">
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -816,7 +845,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D21" t="b">
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="b">
         <v>0</v>
       </c>
     </row>
@@ -834,7 +864,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D22" t="b">
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="b">
         <v>1</v>
       </c>
     </row>
@@ -852,7 +883,8 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D23" t="b">
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -870,7 +902,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D24" t="b">
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -888,7 +921,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D25" t="b">
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="b">
         <v>1</v>
       </c>
     </row>
@@ -906,7 +940,8 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D26" t="b">
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -924,7 +959,8 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D27" t="b">
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="b">
         <v>0</v>
       </c>
     </row>
@@ -942,7 +978,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D28" t="b">
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="b">
         <v>0</v>
       </c>
     </row>
@@ -960,7 +997,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D29" t="b">
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="b">
         <v>1</v>
       </c>
     </row>
@@ -978,7 +1016,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D30" t="b">
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="b">
         <v>0</v>
       </c>
     </row>
@@ -996,7 +1035,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D31" t="b">
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1014,7 +1054,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D32" t="b">
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1032,7 +1073,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D33" t="b">
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1050,7 +1092,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D34" t="b">
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1068,7 +1111,8 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D35" t="b">
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1086,7 +1130,8 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D36" t="b">
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1104,7 +1149,8 @@
           <t>England</t>
         </is>
       </c>
-      <c r="D37" t="b">
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1122,7 +1168,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D38" t="b">
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1140,7 +1187,8 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D39" t="b">
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1158,7 +1206,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D40" t="b">
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1176,7 +1225,8 @@
           <t>England</t>
         </is>
       </c>
-      <c r="D41" t="b">
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1194,7 +1244,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D42" t="b">
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1212,7 +1263,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D43" t="b">
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1230,7 +1282,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D44" t="b">
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1248,7 +1301,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D45" t="b">
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1266,7 +1320,8 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D46" t="b">
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1284,7 +1339,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D47" t="b">
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1302,7 +1358,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D48" t="b">
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1320,7 +1377,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D49" t="b">
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1338,7 +1396,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D50" t="b">
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1356,7 +1415,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D51" t="b">
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1374,7 +1434,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D52" t="b">
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1392,7 +1453,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D53" t="b">
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1410,7 +1472,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D54" t="b">
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1428,7 +1491,8 @@
           <t>England</t>
         </is>
       </c>
-      <c r="D55" t="b">
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1446,7 +1510,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D56" t="b">
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1464,7 +1529,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D57" t="b">
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E57" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1482,7 +1552,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D58" t="b">
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1500,7 +1571,8 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D59" t="b">
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1518,7 +1590,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D60" t="b">
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1536,7 +1609,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D61" t="b">
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1554,7 +1628,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D62" t="b">
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1572,7 +1647,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D63" t="b">
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1590,7 +1666,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D64" t="b">
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1608,7 +1685,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D65" t="b">
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1626,7 +1704,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D66" t="b">
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1644,7 +1723,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D67" t="b">
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1662,7 +1742,8 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D68" t="b">
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1680,7 +1761,8 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D69" t="b">
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1698,7 +1780,8 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D70" t="b">
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1716,7 +1799,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D71" t="b">
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E71" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1734,7 +1822,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D72" t="b">
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1752,7 +1841,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D73" t="b">
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1770,7 +1860,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D74" t="b">
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1788,7 +1879,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D75" t="b">
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1806,7 +1898,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D76" t="b">
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1824,7 +1917,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D77" t="b">
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1842,7 +1936,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D78" t="b">
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1860,7 +1955,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D79" t="b">
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1878,7 +1974,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D80" t="b">
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1896,7 +1993,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D81" t="b">
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1914,7 +2012,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D82" t="b">
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1932,7 +2031,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D83" t="b">
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1950,7 +2050,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D84" t="b">
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1968,7 +2069,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D85" t="b">
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1986,7 +2088,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D86" t="b">
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2004,7 +2107,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D87" t="b">
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2022,7 +2126,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D88" t="b">
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2040,7 +2145,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D89" t="b">
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2058,7 +2164,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D90" t="b">
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2076,7 +2183,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D91" t="b">
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2094,7 +2202,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D92" t="b">
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2112,7 +2221,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D93" t="b">
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2130,7 +2240,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D94" t="b">
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2148,7 +2259,8 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D95" t="b">
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2166,7 +2278,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D96" t="b">
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2184,7 +2297,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D97" t="b">
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2202,7 +2316,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D98" t="b">
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2220,7 +2335,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D99" t="b">
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2238,7 +2354,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D100" t="b">
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E100" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2256,7 +2377,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D101" t="b">
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2274,7 +2396,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D102" t="b">
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2292,7 +2415,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D103" t="b">
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2310,7 +2434,8 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D104" t="b">
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2328,7 +2453,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D105" t="b">
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2346,7 +2472,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D106" t="b">
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2364,7 +2491,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D107" t="b">
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E107" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2382,7 +2514,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D108" t="b">
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2400,7 +2533,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D109" t="b">
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2418,7 +2552,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D110" t="b">
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2436,7 +2571,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D111" t="b">
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E111" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2454,7 +2594,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D112" t="b">
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2472,7 +2613,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D113" t="b">
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2490,7 +2632,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D114" t="b">
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2508,7 +2651,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D115" t="b">
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2526,7 +2670,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D116" t="b">
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2544,7 +2689,12 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D117" t="b">
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E117" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2562,7 +2712,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D118" t="b">
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2580,7 +2731,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D119" t="b">
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2598,7 +2750,8 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D120" t="b">
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2616,7 +2769,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D121" t="b">
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2634,7 +2788,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D122" t="b">
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2652,7 +2807,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D123" t="b">
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2670,7 +2826,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D124" t="b">
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2688,7 +2845,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D125" t="b">
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2706,7 +2864,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D126" t="b">
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2724,7 +2883,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D127" t="b">
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2742,7 +2902,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D128" t="b">
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2760,7 +2921,8 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D129" t="b">
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2778,7 +2940,8 @@
           <t>England</t>
         </is>
       </c>
-      <c r="D130" t="b">
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2796,7 +2959,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D131" t="b">
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2814,7 +2978,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D132" t="b">
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2832,7 +2997,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D133" t="b">
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2850,7 +3016,8 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D134" t="b">
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2868,7 +3035,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D135" t="b">
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2886,7 +3054,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D136" t="b">
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2904,7 +3073,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D137" t="b">
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2922,7 +3092,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D138" t="b">
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2940,7 +3111,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D139" t="b">
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2958,7 +3130,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D140" t="b">
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2976,7 +3149,8 @@
           <t>Britain</t>
         </is>
       </c>
-      <c r="D141" t="b">
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2994,7 +3168,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D142" t="b">
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3012,7 +3187,8 @@
           <t>Rome</t>
         </is>
       </c>
-      <c r="D143" t="b">
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3030,7 +3206,8 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="D144" t="b">
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/german_works_EdB.xlsx
+++ b/data/german_works_EdB.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -477,14 +466,10 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="b">
         <v>1</v>
       </c>
@@ -1146,7 +1131,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1222,7 +1207,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1488,7 +1473,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2937,7 +2922,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>

--- a/data/german_works_EdB.xlsx
+++ b/data/german_works_EdB.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>'Alpharts Tod'</t>
+          <t>Alpharts Tod</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>'Bairisch-österreichisches Buch von Troja' (früher: 'Buch von Troja II')</t>
+          <t>Bairisch-österreichisches Buch von Troja' (früher: 'Buch von Troja II')</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -499,7 +499,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>'Biterolf und Dietleib' ('Biterolf')</t>
+          <t>Biterolf und Dietleib' ('Biterolf')</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>'Breslauer Apollonius'</t>
+          <t>Breslauer Apollonius</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>'Buch von Troja nach Guido de Columnis'</t>
+          <t>Buch von Troja nach Guido de Columnis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>'Cleomades'</t>
+          <t>Cleomades</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>'Daniel'</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>'Der Große Alexander'</t>
+          <t>Der Große Alexander</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>'Der Wunderer'</t>
+          <t>Der Wunderer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>'Die gute Frau'</t>
+          <t>Die gute Frau</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>'Die Königin vom Brennenden See'</t>
+          <t>Die Königin vom Brennenden See</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>'Dietrichs Flucht'</t>
+          <t>Dietrichs Flucht</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>'Eckenlied'</t>
+          <t>Eckenlied</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>'Elsässisches Trojabuch'</t>
+          <t>Elsässisches Trojabuch</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>'Friedrich von Schwaben'</t>
+          <t>Friedrich von Schwaben</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>'Göttweiger Trojanerkrieg'</t>
+          <t>Göttweiger Trojanerkrieg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>'Herzog Ernst' B</t>
+          <t>Herzog Ernst' B</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>'Herzog Ernst' D</t>
+          <t>Herzog Ernst' D</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>'Herzog Ernst' F</t>
+          <t>Herzog Ernst' F</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>'Herzog Ernst' G</t>
+          <t>Herzog Ernst' G</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>'Hildebrandslied'</t>
+          <t>Hildebrandslied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>'Historie van Sent Reinolt'</t>
+          <t>Historie van Sent Reinolt</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>'Johann aus dem Virgiere'</t>
+          <t>Johann aus dem Virgiere</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>'Jüngeres Hildebrandslied'</t>
+          <t>Jüngeres Hildebrandslied</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>'Karl und Elegast'</t>
+          <t>Karl und Elegast</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>'Karlmeinet'-Kompilation</t>
+          <t>Karlmeinet'-Kompilation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>'König Rother'</t>
+          <t>König Rother</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>'Kudrun'</t>
+          <t>Kudrun</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>'Lancelot'</t>
+          <t>Lancelot</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>'Laurin'</t>
+          <t>Laurin</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>'Leipziger Apollonius'</t>
+          <t>Leipziger Apollonius</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>'Lohengrin'</t>
+          <t>Lohengrin</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>'Mai und Beaflor'</t>
+          <t>Mai und Beaflor</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>'Malagis'</t>
+          <t>Malagis</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>'Morant und Galie'</t>
+          <t>Morant und Galie</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>'Münchner Oswald'</t>
+          <t>Münchner Oswald</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>'Nibelungenlied'</t>
+          <t>Nibelungenlied</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>'Ogier von Dänemark'</t>
+          <t>Ogier von Dänemark</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>'Ortnit'</t>
+          <t>Ortnit</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>'Oswald' / 'Berliner Oswald'</t>
+          <t>Oswald' / 'Berliner Oswald</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>'Pontus und Sidonia'</t>
+          <t>Pontus und Sidonia</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>'Rabenschlacht'</t>
+          <t>Rabenschlacht</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>'Rappoltsteiner Parzifal'</t>
+          <t>Rappoltsteiner Parzifal</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>'Reinfried von Braunschweig'</t>
+          <t>Reinfried von Braunschweig</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>'Reinolt von Montelban'</t>
+          <t>Reinolt von Montelban</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>'Rosengarten zu Worms'</t>
+          <t>Rosengarten zu Worms</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>'Salman und Morolf'</t>
+          <t>Salman und Morolf</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>'Sigenot'</t>
+          <t>Sigenot</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>'Tristan als Mönch'</t>
+          <t>Tristan als Mönch</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>'Trojanerkrieg'</t>
+          <t>Trojanerkrieg</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>'Trojanerkrieg'-Fortsetzung</t>
+          <t>Trojanerkrieg'-Fortsetzung</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>'Virginal'</t>
+          <t>Virginal</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>'Walberan'</t>
+          <t>Walberan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>'Wiener Oswald'</t>
+          <t>Wiener Oswald</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>'Wigamur'</t>
+          <t>Wigamur</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>'Willehalm' (Prosaroman)</t>
+          <t>Willehalm' (Prosaroman)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>'Wolfdietrich'</t>
+          <t>Wolfdietrich</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>'Zürcher Buch vom heiligen Karl'</t>
+          <t>Zürcher Buch vom heiligen Karl</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Albrecht von Kemenaten: 'Goldemar'</t>
+          <t>Albrecht von Kemenaten: 'Goldemar</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Albrecht: 'Jüngerer Titurel'</t>
+          <t>Albrecht: 'Jüngerer Titurel</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Berthold von Holle: 'Crane'</t>
+          <t>Berthold von Holle: 'Crane</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Berthold von Holle: 'Demantin'</t>
+          <t>Berthold von Holle: 'Demantin</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Der Pleier: 'Garel von dem blühenden Tal'</t>
+          <t>Der Pleier: 'Garel von dem blühenden Tal</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Der Pleier: 'Meleranz'</t>
+          <t>Der Pleier: 'Meleranz</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Der Pleier: 'Tandareis und Flordibel'</t>
+          <t>Der Pleier: 'Tandareis und Flordibel</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Eilhart von Oberg: 'Tristrant'</t>
+          <t>Eilhart von Oberg: 'Tristrant</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Elisabeth von Nassau-Saarbrücken: 'Herpin'</t>
+          <t>Elisabeth von Nassau-Saarbrücken: 'Herpin</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Elisabeth von Nassau-Saarbrücken: 'Huge Scheppel'</t>
+          <t>Elisabeth von Nassau-Saarbrücken: 'Huge Scheppel</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Elisabeth von Nassau-Saarbrücken: 'Loher und Maller'</t>
+          <t>Elisabeth von Nassau-Saarbrücken: 'Loher und Maller</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Elisabeth von Nassau-Saarbrücken: 'Sibille'</t>
+          <t>Elisabeth von Nassau-Saarbrücken: 'Sibille</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fleck, Konrad: 'Flore und Blanscheflur'</t>
+          <t>Fleck, Konrad: 'Flore und Blanscheflur</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Gottfried von Straßburg: 'Tristan'</t>
+          <t>Gottfried von Straßburg: 'Tristan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Gutevrunt, Heinrich: 'Historia von der vorstorunge troye'</t>
+          <t>Gutevrunt, Heinrich: 'Historia von der vorstorunge troye</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Hartlieb, Johannes: 'Alexander'</t>
+          <t>Hartlieb, Johannes: 'Alexander</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Hartmann von Aue: 'Der arme Heinrich'</t>
+          <t>Hartmann von Aue: 'Der arme Heinrich</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Hartmann von Aue: 'Erec'</t>
+          <t>Hartmann von Aue: 'Erec</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Hartmann von Aue: 'Gregorius'</t>
+          <t>Hartmann von Aue: 'Gregorius</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Hartmann von Aue: 'Iwein'</t>
+          <t>Hartmann von Aue: 'Iwein</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Heinrich von dem Türlin: 'Diu Crône'</t>
+          <t>Heinrich von dem Türlin: 'Diu Crône</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Heinrich von Freiberg: 'Tristan'</t>
+          <t>Heinrich von Freiberg: 'Tristan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Heinrich von Neustadt: 'Apollonius von Tyrland'</t>
+          <t>Heinrich von Neustadt: 'Apollonius von Tyrland</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Heinrich von Veldeke: 'Eneas'</t>
+          <t>Heinrich von Veldeke: 'Eneas</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Herbort von Fritzlar: 'Liet von Troye'</t>
+          <t>Herbort von Fritzlar: 'Liet von Troye</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Johann von Würzburg: 'Wilhelm von Österreich'</t>
+          <t>Johann von Würzburg: 'Wilhelm von Österreich</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Konrad von Stoffeln: 'Gauriel von Muntabel'</t>
+          <t>Konrad von Stoffeln: 'Gauriel von Muntabel</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Konrad von Würzburg: 'Partonopier und Meliur'</t>
+          <t>Konrad von Würzburg: 'Partonopier und Meliur</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Konrad von Würzburg: 'Trojanerkrieg'</t>
+          <t>Konrad von Würzburg: 'Trojanerkrieg</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Mair, Hans, von Nördlingen: 'Buch von Troja'</t>
+          <t>Mair, Hans, von Nördlingen: 'Buch von Troja</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Meister Wichwolt [früher: Babiloth]: 'Cronica Allexandri des grossen konigs'</t>
+          <t>Meister Wichwolt [früher: Babiloth]: 'Cronica Allexandri des grossen konigs</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Otte: 'Eraclius'</t>
+          <t>Otte: 'Eraclius</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Otto II. von Freising: 'Barlaam und Josaphat'</t>
+          <t>Otto II. von Freising: 'Barlaam und Josaphat</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Pfaffe Konrad: 'Rolandslied'</t>
+          <t>Pfaffe Konrad: 'Rolandslied</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Pfaffe Lambrecht: 'Alexanderlied'</t>
+          <t>Pfaffe Lambrecht: 'Alexanderlied</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Rudolf von Ems: 'Alexander'</t>
+          <t>Rudolf von Ems: 'Alexander</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Rudolf von Ems: 'Barlaam und Josaphat'</t>
+          <t>Rudolf von Ems: 'Barlaam und Josaphat</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Rudolf von Ems: 'Der guote Gêrhart'</t>
+          <t>Rudolf von Ems: 'Der guote Gêrhart</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Rudolf von Ems: 'Willehalm von Orlens'</t>
+          <t>Rudolf von Ems: 'Willehalm von Orlens</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Seifrit: 'Alexander'</t>
+          <t>Seifrit: 'Alexander</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Steinhöwel, Heinrich: 'Apollonius'</t>
+          <t>Steinhöwel, Heinrich: 'Apollonius</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Stricker: 'Karl der Große'</t>
+          <t>Stricker: 'Karl der Große</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>'Der Mantel'</t>
+          <t>Der Mantel</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ulrich von dem Türlin: 'Arabel'</t>
+          <t>Ulrich von dem Türlin: 'Arabel</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ulrich von Etzenbach: 'Alexander'</t>
+          <t>Ulrich von Etzenbach: 'Alexander</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ulrich von Etzenbach: 'Alexander-Anhang'</t>
+          <t>Ulrich von Etzenbach: 'Alexander-Anhang</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ulrich von Etzenbach: 'Wilhelm von Wenden'</t>
+          <t>Ulrich von Etzenbach: 'Wilhelm von Wenden</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ulrich von Türheim: 'Rennewart'</t>
+          <t>Ulrich von Türheim: 'Rennewart</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ulrich von Türheim: 'Tristan'</t>
+          <t>Ulrich von Türheim: 'Tristan</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ulrich von Zatzikhoven: 'Lanzelet'</t>
+          <t>Ulrich von Zatzikhoven: 'Lanzelet</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Wirnt von Grafenberg: 'Wigalois'</t>
+          <t>Wirnt von Grafenberg: 'Wigalois</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Wolfram von Eschenbach: 'Parzival'</t>
+          <t>Wolfram von Eschenbach: 'Parzival</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Wolfram von Eschenbach: 'Titurel'</t>
+          <t>Wolfram von Eschenbach: 'Titurel</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Wolfram von Eschenbach: 'Willehalm'</t>
+          <t>Wolfram von Eschenbach: 'Willehalm</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>'Abor und das Meerweib'</t>
+          <t>Abor und das Meerweib</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>'Ainune'</t>
+          <t>Ainune</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>'Alischanz'</t>
+          <t>Alischanz</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>'Athis und Prophilias'</t>
+          <t>Athis und Prophilias</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>'Dietrich und Fasold'</t>
+          <t>Dietrich und Fasold</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>'Dietrich und Wenezlan'</t>
+          <t>Dietrich und Wenezlan</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>'Edolanz'</t>
+          <t>Edolanz</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>'Graf Rudolf'</t>
+          <t>Graf Rudolf</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>'Herzog Ernst' A</t>
+          <t>Herzog Ernst' A</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>'Herzog Ernst' Kl</t>
+          <t>Herzog Ernst' Kl</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>'Hürnen Seyfrid'</t>
+          <t>Hürnen Seyfrid</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>'Karl und Galie'</t>
+          <t>Karl und Galie</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>'Linzer Oswald'</t>
+          <t>Linzer Oswald</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>'Manuel und Amande'</t>
+          <t>Manuel und Amande</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>'Mitteldeutscher Erec'</t>
+          <t>Mitteldeutscher Erec</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>'Niederfränkischer Tristan'</t>
+          <t>Niederfränkischer Tristan</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>'Ospinel'</t>
+          <t>Ospinel</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>'Parcheval'</t>
+          <t>Parcheval</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>'Segremors'</t>
+          <t>Segremors</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>'Trierer Floyris'</t>
+          <t>Trierer Floyris</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>'Waldecker (Marburger) Alexander'</t>
+          <t>Waldecker (Marburger) Alexander</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>'Walther und Hildegund'</t>
+          <t>Walther und Hildegund</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Berthold von Holle: 'Darifant'</t>
+          <t>Berthold von Holle: 'Darifant</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Dietrich von Hopfgarten: 'Wigelis'</t>
+          <t>Dietrich von Hopfgarten: 'Wigelis</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Hans von Bühel: 'Die Königstochter von Frankreich'</t>
+          <t>Hans von Bühel: 'Die Königstochter von Frankreich</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ulrich von Türheim: 'Kliges'</t>
+          <t>Ulrich von Türheim: 'Kliges</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>'Orendel' ('Der Graue Rock')</t>
+          <t>Orendel' ('Der Graue Rock')</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
